--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.3</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T02:28:56+00:00</t>
+    <t>2026-09-03T12:57:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T12:57:16+00:00</t>
+    <t>2026-09-03T15:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T15:50:39+00:00</t>
+    <t>2026-09-03T16:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:38:13+00:00</t>
+    <t>2026-09-03T19:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T19:21:23+00:00</t>
+    <t>2026-09-03T20:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T20:25:33+00:00</t>
+    <t>2026-09-04T14:14:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:14:24+00:00</t>
+    <t>2026-09-04T15:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +123,12 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>234262008</t>
+  </si>
+  <si>
+    <t>396487001</t>
   </si>
 </sst>
 </file>
@@ -434,4 +442,108 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T15:21:29+00:00</t>
+    <t>2026-09-04T16:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:20:32+00:00</t>
+    <t>2026-09-04T19:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T19:28:42+00:00</t>
+    <t>2026-09-05T05:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T05:33:13+00:00</t>
+    <t>2026-09-05T06:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T06:32:59+00:00</t>
+    <t>2026-09-05T07:29:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T07:29:05+00:00</t>
+    <t>2026-09-07T08:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:59:25+00:00</t>
+    <t>2026-09-08T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:16:16+00:00</t>
+    <t>2026-09-09T11:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:12:15+00:00</t>
+    <t>2026-09-09T13:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
+++ b/branches/dev/ValueSet-mii-vs-onko-mamma-operation-sct.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:30:31+00:00</t>
+    <t>2026-09-09T15:05:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
